--- a/Heuristic/data/real/start_generator.xlsx
+++ b/Heuristic/data/real/start_generator.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/real/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B85D085A-19C2-43D8-BE5B-5625CEB2C3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{B85D085A-19C2-43D8-BE5B-5625CEB2C3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD067E41-F37B-44ED-B066-C1D5CFD38FEB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{11746B91-1220-436F-8126-EEF4BA69D2A9}"/>
   </bookViews>
@@ -19,7 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">antigen_demand_80_20_2_scenario!$A$1:$D$25</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1478,7 +1491,7 @@
         <v>278836000</v>
       </c>
       <c r="F8">
-        <f t="shared" ref="F8:F9" si="2">SUM(C8:E8)</f>
+        <f>SUM(C8:E8)</f>
         <v>837500100</v>
       </c>
     </row>
@@ -1491,15 +1504,15 @@
         <v>26052200</v>
       </c>
       <c r="D9">
-        <f t="shared" ref="D9:E9" si="3">D4</f>
+        <f t="shared" ref="D9:E9" si="2">D4</f>
         <v>26626400</v>
       </c>
       <c r="E9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>25785400</v>
       </c>
       <c r="F9">
-        <f t="shared" si="2"/>
+        <f>SUM(C9:E9)</f>
         <v>78464000</v>
       </c>
     </row>

--- a/Heuristic/data/real/start_generator.xlsx
+++ b/Heuristic/data/real/start_generator.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/real/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{B85D085A-19C2-43D8-BE5B-5625CEB2C3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD067E41-F37B-44ED-B066-C1D5CFD38FEB}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{B85D085A-19C2-43D8-BE5B-5625CEB2C3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B39551F1-E032-4647-96C5-A9850FC101EA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{11746B91-1220-436F-8126-EEF4BA69D2A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{11746B91-1220-436F-8126-EEF4BA69D2A9}"/>
   </bookViews>
   <sheets>
     <sheet name="antigen_demand_80_20_2_scenario" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">antigen_demand_80_20_2_scenario!$A$1:$D$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">antigen_demand_80_20_2_scenario!$A$1:$O$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,128 +37,38 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>antigen</t>
   </si>
   <si>
-    <t>demands</t>
-  </si>
-  <si>
-    <t>prob</t>
-  </si>
-  <si>
-    <t>demand_SID</t>
-  </si>
-  <si>
     <t>Diphtheria</t>
   </si>
   <si>
-    <t>[570550200, 619539900, 626455400, 594496900, 595980200, 587103300, 593084700, 587954100, 594707400, 600159000]</t>
-  </si>
-  <si>
-    <t>[671961200, 806951400, 898979700, 834518400, 654102700, 1077658900, 1005487700, 1459749600, 1599437900, 2038009600]</t>
-  </si>
-  <si>
-    <t>HPV</t>
-  </si>
-  <si>
-    <t>[18988200, 18779800, 27460000, 72849500, 92670600, 64703800, 42237000, 42368400, 33730500, 35038500]</t>
-  </si>
-  <si>
-    <t>[27731600, 34629900, 43410500, 45301300, 50540400, 59995100, 67826500, 74584700, 85801100, 88236500]</t>
-  </si>
-  <si>
     <t>Hepatitis_B</t>
   </si>
   <si>
-    <t>[312284600, 343008200, 351717800, 334973600, 334455600, 328430100, 332308900, 328200500, 332214900, 335525400]</t>
-  </si>
-  <si>
-    <t>[346852400, 439985000, 375508800, 327653200, 403873600, 392081200, 494454100, 414794000, 397375400, 506342000]</t>
-  </si>
-  <si>
     <t>Hib</t>
   </si>
   <si>
-    <t>[259536200, 282777100, 287252900, 274027900, 274339400, 270041300, 273119600, 270415600, 273713400, 276715500]</t>
-  </si>
-  <si>
-    <t>[273916300, 329319200, 322078800, 347465800, 351177900, 382722700, 381659000, 390134500, 387135200, 398861500]</t>
-  </si>
-  <si>
     <t>Polio</t>
   </si>
   <si>
-    <t>[522182000, 582182300, 608631800, 590689600, 591743500, 572503000, 130824100, 128516200, 130807300, 132956000]</t>
-  </si>
-  <si>
-    <t>[634745000, 668584400, 704171700, 718635900, 793429000, 789611700, 821959800, 791859400, 794890900, 975111300]</t>
-  </si>
-  <si>
     <t>Measles</t>
   </si>
   <si>
-    <t>[420097000, 358616900, 394831600, 346093200, 377569100, 407486200, 271512200, 386591100, 290515900, 326808200]</t>
-  </si>
-  <si>
-    <t>[328227800, 454099100, 595664200, 719932500, 744078900, 604174000, 1073350100, 764613900, 1053649100, 1020314100]</t>
-  </si>
-  <si>
     <t>Mumps</t>
   </si>
   <si>
-    <t>[26052200, 26626400, 25785400, 25268100, 23536200, 16205400, 18650400, 8909600, 10718500, 12977700]</t>
-  </si>
-  <si>
-    <t>[36420400, 27790700, 22650800, 46488400, 40530500, 34730800, 52074300, 49162500, 57124300, 61173000]</t>
-  </si>
-  <si>
-    <t>PCV</t>
-  </si>
-  <si>
-    <t>[160800200, 186996100, 209165500, 205938500, 220998700, 219106600, 222271100, 217335600, 218764600, 220234300]</t>
-  </si>
-  <si>
-    <t>[235425200, 256608900, 285270700, 378421400, 333352500, 336574700, 438319700, 457157700, 425933000, 659626500]</t>
-  </si>
-  <si>
     <t>Pertussis</t>
   </si>
   <si>
-    <t>[320662700, 347414000, 352464600, 335977000, 334855300, 328035800, 331237500, 328308900, 331462200, 334312000]</t>
-  </si>
-  <si>
-    <t>[367116900, 362365100, 377750200, 367897100, 362899200, 391714800, 368280500, 370618200, 400792100, 427623900]</t>
-  </si>
-  <si>
-    <t>Rotavirus</t>
-  </si>
-  <si>
-    <t>[142479000, 166422100, 173751400, 186328400, 197668300, 205652300, 209552800, 207355600, 209606300, 211802800]</t>
-  </si>
-  <si>
-    <t>[181033600, 251145700, 196360500, 165022000, 316685200, 460136300, 376552300, 568262500, 766224300, 717188900]</t>
-  </si>
-  <si>
     <t>Rubella</t>
   </si>
   <si>
-    <t>[357331300, 254011400, 304621400, 276893800, 291347300, 386542700, 259074600, 385691400, 289592400, 325856600]</t>
-  </si>
-  <si>
-    <t>[320372200, 397600400, 429531300, 414438200, 644513300, 443738900, 632560700, 642992400, 786697900, 698642400]</t>
-  </si>
-  <si>
     <t>Tetanus</t>
   </si>
   <si>
-    <t>[577730200, 626351000, 633278500, 601333100, 598872900, 590040100, 596064300, 590973100, 597764600, 603248400]</t>
-  </si>
-  <si>
-    <t>[644876400, 655930500, 619368000, 698180200, 640386400, 663918000, 632722300, 677456500, 798782900, 731805100]</t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -166,13 +76,471 @@
   </si>
   <si>
     <t>MMR</t>
+  </si>
+  <si>
+    <t>Penta</t>
+  </si>
+  <si>
+    <t>OPV</t>
+  </si>
+  <si>
+    <t>IPV</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>HepB</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>Td</t>
+  </si>
+  <si>
+    <t>DTwP</t>
+  </si>
+  <si>
+    <t>DTwP-Hib</t>
+  </si>
+  <si>
+    <t>Hexa</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Penta"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Diphtheria"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Tetanus"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Pertussis"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hepatitis_B"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hib"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>],</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hexa"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Diphtheria"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Tetanus"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Pertussis"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hepatitis_B"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hib"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Polio"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>],</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DTwP"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Diphtheria"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Tetanus"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Pertussis"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>],</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"DTwP-Hib"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Diphtheria"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Tetanus"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Pertussis"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF8B39"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hib"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF7EDB"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>],</t>
+    </r>
+  </si>
+  <si>
+    <t>post penta</t>
+  </si>
+  <si>
+    <t>post hexa</t>
+  </si>
+  <si>
+    <t>post DT</t>
+  </si>
+  <si>
+    <t>post Td</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,6 +674,24 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF7EDB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF8B39"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="33">
@@ -649,8 +1035,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -707,6 +1102,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1026,377 +1425,439 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE8DDF3-FC1E-4240-BF63-0E194BD6E8FC}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="109.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="10" customWidth="1"/>
+    <col min="7" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="97.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>259536200</v>
+      </c>
+      <c r="C2">
+        <f>MAX(B2-$B$9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>MAX(0,C2-$B$19)</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>282777100</v>
+      </c>
+      <c r="H2">
+        <v>287252900</v>
+      </c>
+      <c r="I2">
+        <v>274027900</v>
+      </c>
+      <c r="J2">
+        <v>274339400</v>
+      </c>
+      <c r="K2">
+        <v>270041300</v>
+      </c>
+      <c r="L2">
+        <v>273119600</v>
+      </c>
+      <c r="M2">
+        <v>270415600</v>
+      </c>
+      <c r="N2">
+        <v>273713400</v>
+      </c>
+      <c r="O2">
+        <v>276715500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>0.8</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+      <c r="B3">
+        <v>312284600</v>
       </c>
       <c r="C3">
-        <v>0.2</v>
+        <f t="shared" ref="C3:C7" si="0">MAX(B3-$B$9,0)</f>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D3:D6" si="1">MAX(0,C3-$B$19)</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>343008200</v>
+      </c>
+      <c r="H3">
+        <v>351717800</v>
+      </c>
+      <c r="I3">
+        <v>334973600</v>
+      </c>
+      <c r="J3">
+        <v>334455600</v>
+      </c>
+      <c r="K3">
+        <v>328430100</v>
+      </c>
+      <c r="L3">
+        <v>332308900</v>
+      </c>
+      <c r="M3">
+        <v>328200500</v>
+      </c>
+      <c r="N3">
+        <v>332214900</v>
+      </c>
+      <c r="O3">
+        <v>335525400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
+      <c r="B4">
+        <v>320662700</v>
       </c>
       <c r="C4">
-        <v>0.8</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="D4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>347414000</v>
+      </c>
+      <c r="H4">
+        <v>352464600</v>
+      </c>
+      <c r="I4">
+        <v>335977000</v>
+      </c>
+      <c r="J4">
+        <v>334855300</v>
+      </c>
+      <c r="K4">
+        <v>328035800</v>
+      </c>
+      <c r="L4">
+        <v>331237500</v>
+      </c>
+      <c r="M4">
+        <v>328308900</v>
+      </c>
+      <c r="N4">
+        <v>331462200</v>
+      </c>
+      <c r="O4">
+        <v>334312000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>522182000</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>146657370</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>65775142</v>
+      </c>
+      <c r="G5">
+        <v>582182300</v>
+      </c>
+      <c r="H5">
+        <v>608631800</v>
+      </c>
+      <c r="I5">
+        <v>590689600</v>
+      </c>
+      <c r="J5">
+        <v>591743500</v>
+      </c>
+      <c r="K5">
+        <v>572503000</v>
+      </c>
+      <c r="L5">
+        <v>130824100</v>
+      </c>
+      <c r="M5">
+        <v>128516200</v>
+      </c>
+      <c r="N5">
+        <v>130807300</v>
+      </c>
+      <c r="O5">
+        <v>132956000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B6">
+        <v>570550200</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>195025570</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>114143342</v>
+      </c>
+      <c r="E6" s="4">
+        <f>MAX(D6-B17,0)</f>
+        <v>4952334.200000003</v>
+      </c>
+      <c r="F6" s="4">
+        <f>E6-B18</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>619539900</v>
+      </c>
+      <c r="H6">
+        <v>626455400</v>
+      </c>
+      <c r="I6">
+        <v>594496900</v>
+      </c>
+      <c r="J6">
+        <v>595980200</v>
+      </c>
+      <c r="K6">
+        <v>587103300</v>
+      </c>
+      <c r="L6">
+        <v>593084700</v>
+      </c>
+      <c r="M6">
+        <v>587954100</v>
+      </c>
+      <c r="N6">
+        <v>594707400</v>
+      </c>
+      <c r="O6">
+        <v>600159000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>0.2</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>0.8</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
+      <c r="B7">
+        <v>577730200</v>
       </c>
       <c r="C7">
-        <v>0.2</v>
+        <f t="shared" si="0"/>
+        <v>202205570</v>
       </c>
       <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>0.8</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <f>MAX(0,C7-$B$19)</f>
+        <v>121323342</v>
+      </c>
+      <c r="E7" s="4">
+        <f>MAX(D7-B17,0)</f>
+        <v>12132334.200000003</v>
+      </c>
+      <c r="F7" s="4">
+        <f>E7-B18</f>
+        <v>7180000</v>
+      </c>
+      <c r="G7">
+        <v>626351000</v>
+      </c>
+      <c r="H7">
+        <v>633278500</v>
+      </c>
+      <c r="I7">
+        <v>601333100</v>
+      </c>
+      <c r="J7">
+        <v>598872900</v>
+      </c>
+      <c r="K7">
+        <v>590040100</v>
+      </c>
+      <c r="L7">
+        <v>596064300</v>
+      </c>
+      <c r="M7">
+        <v>590973100</v>
+      </c>
+      <c r="N7">
+        <v>597764600</v>
+      </c>
+      <c r="O7">
+        <v>603248400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4">
+        <f>B7*0.65</f>
+        <v>375524630</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
-        <v>0.2</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="B13" s="4">
+        <f>D5</f>
+        <v>65775142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B14" s="4">
+        <f>F7</f>
+        <v>7180000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10">
-        <v>0.8</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B15" s="4">
+        <f>B3*0.01</f>
+        <v>3122846</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="4">
+        <f>B2*0.01</f>
+        <v>2595362</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11">
-        <v>0.2</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B17" s="4">
+        <f>D7*0.9</f>
+        <v>109191007.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12">
-        <v>0.8</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13">
-        <v>0.2</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B18" s="4">
+        <f>E6</f>
+        <v>4952334.200000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B19" s="4">
+        <f>C7*0.4</f>
+        <v>80882228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C14">
-        <v>0.8</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C15">
-        <v>0.2</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B16" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C16">
-        <v>0.8</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17">
-        <v>0.2</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18">
-        <v>0.8</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19">
-        <v>0.2</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20">
-        <v>0.8</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21">
-        <v>0.2</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22">
-        <v>0.8</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23">
-        <v>0.2</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24">
-        <v>0.8</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25">
-        <v>0.2</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D25" xr:uid="{DCE8DDF3-FC1E-4240-BF63-0E194BD6E8FC}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Measles"/>
-        <filter val="Mumps"/>
-        <filter val="Rubella"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:O7" xr:uid="{DCE8DDF3-FC1E-4240-BF63-0E194BD6E8FC}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O7">
+      <sortCondition ref="B1:B7"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1413,7 +1874,7 @@
   <sheetData>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>420097000</v>
@@ -1427,7 +1888,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>26052200</v>
@@ -1441,7 +1902,7 @@
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>357331300</v>
@@ -1455,7 +1916,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <f>C3-C8-C9</f>
@@ -1476,7 +1937,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <f>C5-C9</f>
@@ -1497,7 +1958,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C9">
         <f>C4</f>
